--- a/data/trans_orig/IP31KM15_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM15_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22921</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35733</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23184</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15218</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30689</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53758</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>45515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65686</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24103</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17982</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30794</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30515</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23010</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38481</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27770</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58285</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69897</t>
+          <t>54105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>257200</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>234787</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>277656</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>55,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>253817</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>205904</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>276295</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>56,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>273215</t>
+          <t>251644</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>248485</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>269605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>527032</t>
+          <t>508844</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>470498</t>
+          <t>480956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>561866</t>
+          <t>536364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>209223</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>188767</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>231636</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>198015</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>175537</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>245928</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>232035</t>
+          <t>173022</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207785</t>
+          <t>155061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256765</t>
+          <t>189956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>430050</t>
+          <t>382246</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395216</t>
+          <t>354726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>486584</t>
+          <t>410134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93295</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81320</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>104215</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83442</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73236</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93632</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>57,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>84109</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>73307</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>93842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>185245</t>
+          <t>177403</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168848</t>
+          <t>162476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200647</t>
+          <t>192493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73391</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85366</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>62744</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52554</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72950</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66270</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90867</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>142079</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126677</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158476</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>380108</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>356711</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>407480</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>534</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>360443</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>309938</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>387122</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>359949</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>378260</t>
+          <t>338435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>431631</t>
+          <t>381826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>766036</t>
+          <t>740057</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>713617</t>
+          <t>707705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>803824</t>
+          <t>772332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>306716</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>279344</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>330113</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>380</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>291274</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>264595</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>341779</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>339140</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313102</t>
+          <t>235885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366473</t>
+          <t>279276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>564478</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>532203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>682833</t>
+          <t>596830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
